--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1773,22 +1773,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1799,12 +1803,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1814,16 +1818,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1834,23 +1838,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1870,26 +1878,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1905,12 +1913,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1940,18 +1948,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1971,12 +1979,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2006,26 +2014,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2036,27 +2044,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2076,22 +2080,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2106,23 +2106,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2208,22 +2208,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2239,18 +2243,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2270,26 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G442"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1428,26 +1428,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1783,16 +1783,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1808,22 +1808,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1838,27 +1834,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1878,26 +1870,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1913,12 +1905,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1948,22 +1940,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1979,12 +1975,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1994,7 +1990,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2014,26 +2010,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2044,23 +2040,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2075,23 +2075,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2111,18 +2111,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2208,26 +2208,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2243,22 +2239,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2274,18 +2274,18 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12462,6 +12462,29 @@
         <v>3</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2025-02-26 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
